--- a/data/trans_orig/P36BPD07_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023</t>
+          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85250</t>
+          <t>85957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120254</t>
+          <t>122354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55402</t>
+          <t>54692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79193</t>
+          <t>80294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148471</t>
+          <t>149905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191960</t>
+          <t>193054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384958</t>
+          <t>382858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419962</t>
+          <t>419255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>366185</t>
+          <t>365084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389976</t>
+          <t>390686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758630</t>
+          <t>757536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>802119</t>
+          <t>800685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96646</t>
+          <t>95980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133748</t>
+          <t>133410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65859</t>
+          <t>65816</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94906</t>
+          <t>94318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170637</t>
+          <t>171209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>216863</t>
+          <t>219030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>318465</t>
+          <t>318803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355567</t>
+          <t>356233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287674</t>
+          <t>288262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316721</t>
+          <t>316764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617930</t>
+          <t>615763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>664156</t>
+          <t>663584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48392</t>
+          <t>47057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>204053</t>
+          <t>207932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>28634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46522</t>
+          <t>45075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67628</t>
+          <t>68777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235934</t>
+          <t>234559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463374</t>
+          <t>459495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619035</t>
+          <t>620370</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120389</t>
+          <t>121836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137947</t>
+          <t>138277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598403</t>
+          <t>599778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>766709</t>
+          <t>765560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>274965</t>
+          <t>268646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>345563</t>
+          <t>341641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90888</t>
+          <t>87631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240018</t>
+          <t>241931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350504</t>
+          <t>342374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>561775</t>
+          <t>567434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>688337</t>
+          <t>692259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>758935</t>
+          <t>765254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>736691</t>
+          <t>734778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>885821</t>
+          <t>889078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1448834</t>
+          <t>1443175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1660105</t>
+          <t>1668235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140023</t>
+          <t>140550</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186473</t>
+          <t>187521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>132834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209925</t>
+          <t>212673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>277883</t>
+          <t>282320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>383847</t>
+          <t>388093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>286583</t>
+          <t>285535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333033</t>
+          <t>332506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>631248</t>
+          <t>628500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>707196</t>
+          <t>708339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>930383</t>
+          <t>926137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1036347</t>
+          <t>1031910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92282</t>
+          <t>93287</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180720</t>
+          <t>180445</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>226807</t>
+          <t>229425</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>239026</t>
+          <t>242143</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>310901</t>
+          <t>306542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147129</t>
+          <t>146124</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191252</t>
+          <t>192750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>534016</t>
+          <t>531398</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>580103</t>
+          <t>580378</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>689333</t>
+          <t>693692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>761208</t>
+          <t>758091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>689252</t>
+          <t>649379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>968369</t>
+          <t>970560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>628090</t>
+          <t>615654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>827585</t>
+          <t>822700</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1410036</t>
+          <t>1393447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1767239</t>
+          <t>1758954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2402850</t>
+          <t>2400659</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2681967</t>
+          <t>2721840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2745990</t>
+          <t>2750875</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2945485</t>
+          <t>2957921</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5177554</t>
+          <t>5185839</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5534757</t>
+          <t>5551346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD07_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>102124</t>
+          <t>115477</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>97000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122354</t>
+          <t>135029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67188</t>
+          <t>77954</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54692</t>
+          <t>64008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80294</t>
+          <t>93625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>193432</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149905</t>
+          <t>170593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193054</t>
+          <t>221103</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>403088</t>
+          <t>435141</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382858</t>
+          <t>415589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419255</t>
+          <t>453618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>378190</t>
+          <t>408380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365084</t>
+          <t>392709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390686</t>
+          <t>422326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>781277</t>
+          <t>843520</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757536</t>
+          <t>815849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>800685</t>
+          <t>866359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445378</t>
+          <t>486334</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445378</t>
+          <t>486334</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445378</t>
+          <t>486334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950590</t>
+          <t>1036952</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950590</t>
+          <t>1036952</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950590</t>
+          <t>1036952</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>113995</t>
+          <t>124099</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95980</t>
+          <t>105417</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133410</t>
+          <t>143853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79217</t>
+          <t>89828</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65816</t>
+          <t>76188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94318</t>
+          <t>107296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>213928</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171209</t>
+          <t>187280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>219030</t>
+          <t>240898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>338218</t>
+          <t>359113</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>318803</t>
+          <t>339359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356233</t>
+          <t>377795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>303363</t>
+          <t>333315</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288262</t>
+          <t>315847</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316764</t>
+          <t>346955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>641580</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>615763</t>
+          <t>665457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>663584</t>
+          <t>719075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>124276</t>
+          <t>139593</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47057</t>
+          <t>119276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207932</t>
+          <t>160043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>33986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45075</t>
+          <t>53267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>161284</t>
+          <t>181924</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68777</t>
+          <t>157996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234559</t>
+          <t>204111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>543151</t>
+          <t>331154</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459495</t>
+          <t>310704</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620370</t>
+          <t>351471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>129903</t>
+          <t>145166</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121836</t>
+          <t>134230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138277</t>
+          <t>153511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>673053</t>
+          <t>476320</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>599778</t>
+          <t>454133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>765560</t>
+          <t>500248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>308217</t>
+          <t>332133</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>268646</t>
+          <t>297453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>341641</t>
+          <t>365446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>183161</t>
+          <t>209300</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87631</t>
+          <t>186519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241931</t>
+          <t>233082</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>491378</t>
+          <t>541433</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342374</t>
+          <t>503928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>567434</t>
+          <t>582690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>725683</t>
+          <t>798637</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>692259</t>
+          <t>765324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>765254</t>
+          <t>833317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>793548</t>
+          <t>649915</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>734778</t>
+          <t>626133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>889078</t>
+          <t>672696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1519231</t>
+          <t>1448552</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443175</t>
+          <t>1407295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1668235</t>
+          <t>1486057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033900</t>
+          <t>1130770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033900</t>
+          <t>1130770</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033900</t>
+          <t>1130770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976709</t>
+          <t>859215</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976709</t>
+          <t>859215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976709</t>
+          <t>859215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010609</t>
+          <t>1989985</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010609</t>
+          <t>1989985</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010609</t>
+          <t>1989985</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>163147</t>
+          <t>193679</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140550</t>
+          <t>170190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187521</t>
+          <t>217882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>181689</t>
+          <t>207573</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132834</t>
+          <t>186215</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>212673</t>
+          <t>228976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>344836</t>
+          <t>401252</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>282320</t>
+          <t>368966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388093</t>
+          <t>433624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>309909</t>
+          <t>372266</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>285535</t>
+          <t>348063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332506</t>
+          <t>395755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>659484</t>
+          <t>622533</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>628500</t>
+          <t>601130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>708339</t>
+          <t>643891</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>969394</t>
+          <t>994799</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>926137</t>
+          <t>962427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1031910</t>
+          <t>1027085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473056</t>
+          <t>565945</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473056</t>
+          <t>565945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473056</t>
+          <t>565945</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841173</t>
+          <t>830106</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841173</t>
+          <t>830106</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841173</t>
+          <t>830106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314230</t>
+          <t>1396051</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314230</t>
+          <t>1396051</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314230</t>
+          <t>1396051</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69149</t>
+          <t>78251</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46661</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93287</t>
+          <t>101183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>204223</t>
+          <t>234283</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180445</t>
+          <t>209011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>229425</t>
+          <t>260075</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>273372</t>
+          <t>312534</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>242143</t>
+          <t>281260</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>306542</t>
+          <t>350760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>170262</t>
+          <t>157778</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146124</t>
+          <t>134846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192750</t>
+          <t>178129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>556600</t>
+          <t>609387</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>531398</t>
+          <t>583595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>580378</t>
+          <t>634659</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>726862</t>
+          <t>767165</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>693692</t>
+          <t>728939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>758091</t>
+          <t>798439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>239411</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239411</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239411</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760823</t>
+          <t>843670</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760823</t>
+          <t>843670</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760823</t>
+          <t>843670</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000234</t>
+          <t>1079699</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000234</t>
+          <t>1079699</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000234</t>
+          <t>1079699</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>880908</t>
+          <t>983234</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>649379</t>
+          <t>925133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>970560</t>
+          <t>1039059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>752487</t>
+          <t>861268</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>615654</t>
+          <t>813982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>822700</t>
+          <t>906289</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1633395</t>
+          <t>1844502</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1393447</t>
+          <t>1770482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1758954</t>
+          <t>1917699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2490311</t>
+          <t>2454087</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2400659</t>
+          <t>2398262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2721840</t>
+          <t>2512188</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2821088</t>
+          <t>2768697</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2750875</t>
+          <t>2723676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2957921</t>
+          <t>2815983</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5311398</t>
+          <t>5222784</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5185839</t>
+          <t>5149587</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5551346</t>
+          <t>5296804</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371219</t>
+          <t>3437321</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371219</t>
+          <t>3437321</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371219</t>
+          <t>3437321</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573575</t>
+          <t>3629965</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573575</t>
+          <t>3629965</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573575</t>
+          <t>3629965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6944793</t>
+          <t>7067286</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6944793</t>
+          <t>7067286</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6944793</t>
+          <t>7067286</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
